--- a/etf_holdings/2026-09-07_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-07_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR8"/>
+  <dimension ref="A1:BB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,200 +439,250 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>00981A_異動類型</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>00981A_調整方向</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>00981A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>00981A_權重_今日</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>00981A_權重變化</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>00981A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>00981A_股數_今日</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>00981A_股數變化</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>00982A_異動類型</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>00982A_調整方向</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>00982A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>00982A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>00982A_權重_昨日</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>00982A_權重_今日</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>00982A_權重變化</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>00982A_股數_昨日</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>00982A_股數_今日</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>00982A_股數變化</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>00403A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>00403A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>00403A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>00403A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>00403A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>00403A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>00403A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>00403A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>00985A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00985A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00985A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00985A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00985A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00985A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00985A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00985A_股數變化</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>00400A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00400A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00400A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00400A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00400A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00400A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00400A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -657,108 +707,108 @@
           <t>00403A,00982A</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>1.31%</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>+0.12%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="V2" t="n">
         <v>5205000</v>
       </c>
-      <c r="M2" t="n">
+      <c r="W2" t="n">
         <v>5190000</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>-15,000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>4.05%</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>4.90%</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>+0.85%</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AF2" t="n">
         <v>50000000</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AG2" t="n">
         <v>55000000</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5,000,000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -769,6 +819,16 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -789,100 +849,110 @@
           <t>00982A,00985A</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>微星</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>微星</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1.35%</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1.31%</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>-0.04%</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="V3" t="n">
         <v>4322000</v>
       </c>
-      <c r="M3" t="n">
+      <c r="W3" t="n">
         <v>4308000</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>-14,000</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>微星科技</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1.86%</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>1213000</v>
-      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>微星科技</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>1.86%</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>1213000</v>
+      </c>
       <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -903,62 +973,62 @@
           <t>00400A,00982A</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>台光電</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>台光電</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>3.30%</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>3.31%</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>+0.01%</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="V4" t="n">
         <v>315000</v>
       </c>
-      <c r="M4" t="n">
+      <c r="W4" t="n">
         <v>314000</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>-1,000</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -969,48 +1039,58 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>台光電</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>台光電</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>2.29%</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>3.30%</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>+1.01%</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AZ4" t="n">
         <v>123000</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="BA4" t="n">
         <v>175000</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>52,000</t>
         </is>
@@ -1035,128 +1115,138 @@
           <t>00982A,00985A</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>研華</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>研華</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2.02%</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1.91%</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>-0.11%</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="V5" t="n">
         <v>1466000</v>
       </c>
-      <c r="M5" t="n">
+      <c r="W5" t="n">
         <v>1463000</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>-3,000</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>研華</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>研華</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>2.04%</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>3.00%</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>+0.96%</t>
         </is>
       </c>
-      <c r="AF5" t="n">
+      <c r="AP5" t="n">
         <v>313000</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AQ5" t="n">
         <v>444000</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>131,000</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1164,131 +1254,141 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00400A,00403A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>3.39%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2.84%</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-0.55%</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>736000</v>
-      </c>
-      <c r="W6" t="n">
-        <v>686000</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-50,000</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7.94%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8.57%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>5088000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5186000</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>98,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>3.92%</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2.77%</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>-1.15%</t>
-        </is>
-      </c>
-      <c r="AP6" t="n">
-        <v>154000</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>121000</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-33,000</t>
-        </is>
-      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>5.80%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>6.55%</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>+0.75%</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>2110000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2210000</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1296,55 +1396,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00400A,00982A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2.58%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2.45%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>374000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>373000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
+          <t>00400A,00403A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -1355,72 +1419,118 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>4.13%</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>4.42%</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>+0.29%</t>
-        </is>
-      </c>
-      <c r="AP7" t="n">
-        <v>336000</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>377000</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>41,000</t>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>-0.55%</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>736000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>686000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>3.92%</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2.77%</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>-1.15%</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>154000</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>121000</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-33,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1428,99 +1538,63 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00403A,00982A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+          <t>00400A,00982A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.07%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1.12%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>942000</v>
-      </c>
-      <c r="M8" t="n">
-        <v>939000</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-3,000</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>4500000</v>
+        <v>374000</v>
       </c>
       <c r="W8" t="n">
-        <v>4000000</v>
+        <v>373000</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-500,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1543,6 +1617,460 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>4.13%</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>4.42%</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>336000</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>377000</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>41,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00403A,00982A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>942000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>939000</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-500,000</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00981A,00985A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2157000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2712000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>555,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>臻鼎科技控股</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-260,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1.41%</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1580000</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>-157,000</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
